--- a/Honorarios_Fevereiro_2026.xlsx
+++ b/Honorarios_Fevereiro_2026.xlsx
@@ -765,10 +765,10 @@
         <v>1340.2</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>776.48</v>
+        <v>748.8</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>563.6799999999999</v>
+        <v>591.36</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>592.5</v>
+        <v>533.25</v>
       </c>
     </row>
     <row r="12">
@@ -1017,10 +1017,10 @@
         <v>193101.27</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>120080.76</v>
+        <v>120053.08</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>73020.34</v>
+        <v>72988.77</v>
       </c>
     </row>
   </sheetData>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Fotona</t>
+          <t>Fotona (Indicação)</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         <v>1340.2</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>776.48</v>
+        <v>748.8</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>0.5794</v>
+        <v>0.5587</v>
       </c>
     </row>
     <row r="8">
@@ -5303,10 +5303,10 @@
         <v>69.125</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T24" s="10" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="11" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="25">
@@ -5393,10 +5393,10 @@
         <v>69.125</v>
       </c>
       <c r="R25" s="15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S25" s="14" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T25" s="13" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="14" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="26">
@@ -5483,10 +5483,10 @@
         <v>69.125</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T26" s="10" t="n">
         <v>0</v>
@@ -5495,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="11" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="27">
@@ -5573,10 +5573,10 @@
         <v>69.125</v>
       </c>
       <c r="R27" s="15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S27" s="14" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T27" s="13" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="14" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="28">
@@ -5663,10 +5663,10 @@
         <v>69.125</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T28" s="10" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="11" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="29">
@@ -5753,10 +5753,10 @@
         <v>69.125</v>
       </c>
       <c r="R29" s="15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S29" s="14" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T29" s="13" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="14" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="30">
@@ -5843,10 +5843,10 @@
         <v>69.125</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S30" s="11" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T30" s="10" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="11" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="31">
@@ -5933,10 +5933,10 @@
         <v>69.125</v>
       </c>
       <c r="R31" s="15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>38.02</v>
+        <v>34.56</v>
       </c>
       <c r="T31" s="13" t="n">
         <v>0</v>
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="14" t="n">
-        <v>31.1</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="32">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Fotona</t>
+          <t>Fotona (Indicação)</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
@@ -8181,13 +8181,13 @@
         <v>0</v>
       </c>
       <c r="T56" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0</v>
+        <v>59.25</v>
       </c>
       <c r="V56" s="11" t="n">
-        <v>592.5</v>
+        <v>533.25</v>
       </c>
     </row>
     <row r="57">
@@ -54438,7 +54438,7 @@
         <v>1340.2</v>
       </c>
       <c r="L13" s="21" t="n">
-        <v>776.48</v>
+        <v>748.8</v>
       </c>
     </row>
   </sheetData>
